--- a/data/rawdata/dataMappingAlltissues.xlsx
+++ b/data/rawdata/dataMappingAlltissues.xlsx
@@ -1685,7 +1685,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:T55"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.5"/>
